--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/116.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/116.xlsx
@@ -426,13 +426,13 @@
         <v>-0.6678748361472919</v>
       </c>
       <c r="E2">
-        <v>-8.279383934087271</v>
+        <v>-8.243871640919119</v>
       </c>
       <c r="F2">
-        <v>-6.513269954515175</v>
+        <v>-6.834058693996448</v>
       </c>
       <c r="G2">
-        <v>-9.238935909299252</v>
+        <v>-8.502213726080921</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.098495371617189</v>
       </c>
       <c r="E3">
-        <v>-8.988764858914823</v>
+        <v>-9.504793529036878</v>
       </c>
       <c r="F3">
-        <v>-6.327583999268208</v>
+        <v>-6.786127834465673</v>
       </c>
       <c r="G3">
-        <v>-9.430394689471923</v>
+        <v>-8.789721363984468</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.657099564255458</v>
       </c>
       <c r="E4">
-        <v>-8.64139014626044</v>
+        <v>-10.65037065570526</v>
       </c>
       <c r="F4">
-        <v>-6.585567317334422</v>
+        <v>-6.520362185530991</v>
       </c>
       <c r="G4">
-        <v>-8.74573745594971</v>
+        <v>-8.923808389961568</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.238798783137281</v>
       </c>
       <c r="E5">
-        <v>-11.01013980171864</v>
+        <v>-11.59972447514728</v>
       </c>
       <c r="F5">
-        <v>-6.567769630256713</v>
+        <v>-6.775852354559823</v>
       </c>
       <c r="G5">
-        <v>-8.444636718061917</v>
+        <v>-8.745922846499909</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.808795939051889</v>
       </c>
       <c r="E6">
-        <v>-10.20809271327213</v>
+        <v>-11.09617627939037</v>
       </c>
       <c r="F6">
-        <v>-6.613299591619682</v>
+        <v>-6.863504142155735</v>
       </c>
       <c r="G6">
-        <v>-8.978488670633709</v>
+        <v>-9.451681497289437</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.313108169489674</v>
       </c>
       <c r="E7">
-        <v>-12.35206703288561</v>
+        <v>-12.6162627349671</v>
       </c>
       <c r="F7">
-        <v>-6.453790315522536</v>
+        <v>-6.686907075157476</v>
       </c>
       <c r="G7">
-        <v>-9.298466139186427</v>
+        <v>-8.728290880957751</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.71697485580075</v>
       </c>
       <c r="E8">
-        <v>-13.19131553530513</v>
+        <v>-14.19972065580717</v>
       </c>
       <c r="F8">
-        <v>-6.511908363354375</v>
+        <v>-6.702544587366526</v>
       </c>
       <c r="G8">
-        <v>-8.76599799465005</v>
+        <v>-9.30053854069401</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.988826942535291</v>
       </c>
       <c r="E9">
-        <v>-13.62938199691113</v>
+        <v>-14.40389596339101</v>
       </c>
       <c r="F9">
-        <v>-6.531479009204419</v>
+        <v>-6.419374406347643</v>
       </c>
       <c r="G9">
-        <v>-8.990668167672688</v>
+        <v>-8.794385922649299</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.111960423857665</v>
       </c>
       <c r="E10">
-        <v>-15.66436047563399</v>
+        <v>-15.76182229322707</v>
       </c>
       <c r="F10">
-        <v>-6.432904005983242</v>
+        <v>-6.572434040104161</v>
       </c>
       <c r="G10">
-        <v>-7.822446168320211</v>
+        <v>-9.347842925904656</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.078766890891803</v>
       </c>
       <c r="E11">
-        <v>-15.94953659779302</v>
+        <v>-15.52711601388352</v>
       </c>
       <c r="F11">
-        <v>-6.456922489896797</v>
+        <v>-6.662355674203376</v>
       </c>
       <c r="G11">
-        <v>-8.210902271352753</v>
+        <v>-8.811412058357771</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.897487194775627</v>
       </c>
       <c r="E12">
-        <v>-16.09826979810095</v>
+        <v>-16.1428163969144</v>
       </c>
       <c r="F12">
-        <v>-6.520640521845629</v>
+        <v>-6.953635617288746</v>
       </c>
       <c r="G12">
-        <v>-7.993485503606657</v>
+        <v>-7.219575962345693</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.585420633727643</v>
       </c>
       <c r="E13">
-        <v>-16.95767906680262</v>
+        <v>-16.2933066451373</v>
       </c>
       <c r="F13">
-        <v>-6.461700530643677</v>
+        <v>-6.453303721880017</v>
       </c>
       <c r="G13">
-        <v>-7.055439114508627</v>
+        <v>-7.396663664332387</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.172443202730308</v>
       </c>
       <c r="E14">
-        <v>-17.74694227312548</v>
+        <v>-19.06151752128612</v>
       </c>
       <c r="F14">
-        <v>-6.311817019100572</v>
+        <v>-6.582060992437639</v>
       </c>
       <c r="G14">
-        <v>-6.236373732092003</v>
+        <v>-5.977965789478652</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.696142995292512</v>
       </c>
       <c r="E15">
-        <v>-19.36061870101873</v>
+        <v>-19.56858434134699</v>
       </c>
       <c r="F15">
-        <v>-6.423261612517089</v>
+        <v>-6.653283018940303</v>
       </c>
       <c r="G15">
-        <v>-5.786881100951919</v>
+        <v>-7.275593703415701</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.199554565181013</v>
       </c>
       <c r="E16">
-        <v>-19.59118142664526</v>
+        <v>-18.30609560122258</v>
       </c>
       <c r="F16">
-        <v>-6.274125214239593</v>
+        <v>-6.514560278909778</v>
       </c>
       <c r="G16">
-        <v>-5.351855553818449</v>
+        <v>-6.066873800481319</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.728573777203109</v>
       </c>
       <c r="E17">
-        <v>-20.92177388737103</v>
+        <v>-21.09617447835443</v>
       </c>
       <c r="F17">
-        <v>-6.065972015023245</v>
+        <v>-6.525953855191929</v>
       </c>
       <c r="G17">
-        <v>-4.940550065473857</v>
+        <v>-4.806420002404746</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.318249502903917</v>
       </c>
       <c r="E18">
-        <v>-22.03566528140774</v>
+        <v>-22.02217495733889</v>
       </c>
       <c r="F18">
-        <v>-6.015123969196231</v>
+        <v>-5.890852149717613</v>
       </c>
       <c r="G18">
-        <v>-4.364680668917635</v>
+        <v>-4.222194788907403</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.9966626786012648</v>
       </c>
       <c r="E19">
-        <v>-23.14158656119096</v>
+        <v>-23.08348623967255</v>
       </c>
       <c r="F19">
-        <v>-5.497549871559634</v>
+        <v>-5.746837852297126</v>
       </c>
       <c r="G19">
-        <v>-4.757500070970936</v>
+        <v>-4.49107067651593</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.7761422709764404</v>
       </c>
       <c r="E20">
-        <v>-23.72226825472053</v>
+        <v>-22.91919320267427</v>
       </c>
       <c r="F20">
-        <v>-5.280115759752333</v>
+        <v>-5.515130590926928</v>
       </c>
       <c r="G20">
-        <v>-3.728443474452801</v>
+        <v>-4.424280420261134</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6551965116133658</v>
       </c>
       <c r="E21">
-        <v>-23.85204979130635</v>
+        <v>-24.22539077392072</v>
       </c>
       <c r="F21">
-        <v>-5.239509540080466</v>
+        <v>-5.477979225709591</v>
       </c>
       <c r="G21">
-        <v>-3.976618520804266</v>
+        <v>-4.105670207016136</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.6245655943278382</v>
       </c>
       <c r="E22">
-        <v>-25.17933193753251</v>
+        <v>-25.85949967653658</v>
       </c>
       <c r="F22">
-        <v>-4.604360323428686</v>
+        <v>-5.076625386677518</v>
       </c>
       <c r="G22">
-        <v>-3.538921363420604</v>
+        <v>-3.346098638485754</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.6621749031516085</v>
       </c>
       <c r="E23">
-        <v>-26.14828499247973</v>
+        <v>-25.88777093976647</v>
       </c>
       <c r="F23">
-        <v>-4.592585469947394</v>
+        <v>-4.988367831568951</v>
       </c>
       <c r="G23">
-        <v>-3.852188356165219</v>
+        <v>-4.128708293423924</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.7487059679824472</v>
       </c>
       <c r="E24">
-        <v>-25.66730671117704</v>
+        <v>-26.01503464480403</v>
       </c>
       <c r="F24">
-        <v>-4.555877542386381</v>
+        <v>-4.58370404717361</v>
       </c>
       <c r="G24">
-        <v>-3.267175232829529</v>
+        <v>-4.078920999058824</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.8645472141799324</v>
       </c>
       <c r="E25">
-        <v>-26.32953263616272</v>
+        <v>-27.43442142387219</v>
       </c>
       <c r="F25">
-        <v>-4.383386628900379</v>
+        <v>-4.785430171858625</v>
       </c>
       <c r="G25">
-        <v>-3.78441486788526</v>
+        <v>-3.383226406708681</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.9938617024638688</v>
       </c>
       <c r="E26">
-        <v>-26.06972049692065</v>
+        <v>-25.8250923310263</v>
       </c>
       <c r="F26">
-        <v>-4.218963905200582</v>
+        <v>-3.877461480124797</v>
       </c>
       <c r="G26">
-        <v>-4.805099094734577</v>
+        <v>-4.093450983430685</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.130081193116616</v>
       </c>
       <c r="E27">
-        <v>-26.1720006108579</v>
+        <v>-26.99036831962805</v>
       </c>
       <c r="F27">
-        <v>-4.232949612139827</v>
+        <v>-3.580484946861591</v>
       </c>
       <c r="G27">
-        <v>-4.66195441616203</v>
+        <v>-4.395548195525799</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.2666576141855</v>
       </c>
       <c r="E28">
-        <v>-26.22093077251077</v>
+        <v>-26.77738060162529</v>
       </c>
       <c r="F28">
-        <v>-4.204831705464158</v>
+        <v>-4.067135602793317</v>
       </c>
       <c r="G28">
-        <v>-4.406304157982891</v>
+        <v>-4.703375961949392</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.404053872137887</v>
       </c>
       <c r="E29">
-        <v>-26.32216028047824</v>
+        <v>-27.83378301813463</v>
       </c>
       <c r="F29">
-        <v>-3.815785636953922</v>
+        <v>-3.905892960571723</v>
       </c>
       <c r="G29">
-        <v>-4.642024932015618</v>
+        <v>-4.777823510036521</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.542292916900191</v>
       </c>
       <c r="E30">
-        <v>-25.32073353842202</v>
+        <v>-26.08682454324762</v>
       </c>
       <c r="F30">
-        <v>-3.720956494149239</v>
+        <v>-4.403569377086739</v>
       </c>
       <c r="G30">
-        <v>-3.963419375739192</v>
+        <v>-4.198372103206808</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.680071253119165</v>
       </c>
       <c r="E31">
-        <v>-25.81656974294387</v>
+        <v>-25.31332948341947</v>
       </c>
       <c r="F31">
-        <v>-3.988855394952019</v>
+        <v>-3.868937974887901</v>
       </c>
       <c r="G31">
-        <v>-4.914406687350233</v>
+        <v>-5.055882850970987</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.818502919959205</v>
       </c>
       <c r="E32">
-        <v>-25.29487595183822</v>
+        <v>-24.84788839643711</v>
       </c>
       <c r="F32">
-        <v>-3.951839436590452</v>
+        <v>-3.921948571142448</v>
       </c>
       <c r="G32">
-        <v>-4.624048669737375</v>
+        <v>-4.298506174133143</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.954435281798771</v>
       </c>
       <c r="E33">
-        <v>-24.74155076978899</v>
+        <v>-24.16498093065839</v>
       </c>
       <c r="F33">
-        <v>-3.951148940811321</v>
+        <v>-4.148506412728596</v>
       </c>
       <c r="G33">
-        <v>-4.71619108373191</v>
+        <v>-4.261616765189044</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.084814988012625</v>
       </c>
       <c r="E34">
-        <v>-24.50353417594584</v>
+        <v>-26.53253054050456</v>
       </c>
       <c r="F34">
-        <v>-4.133876929334725</v>
+        <v>-4.605958282697365</v>
       </c>
       <c r="G34">
-        <v>-3.624032178689728</v>
+        <v>-5.002851221977402</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.203540161619191</v>
       </c>
       <c r="E35">
-        <v>-24.00582771165882</v>
+        <v>-24.25942678456236</v>
       </c>
       <c r="F35">
-        <v>-4.180676230988918</v>
+        <v>-4.112182533852077</v>
       </c>
       <c r="G35">
-        <v>-4.488276576080785</v>
+        <v>-4.216980679683051</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.300965769050189</v>
       </c>
       <c r="E36">
-        <v>-23.81219016309083</v>
+        <v>-23.65929529516986</v>
       </c>
       <c r="F36">
-        <v>-4.069565007667602</v>
+        <v>-4.163470849923583</v>
       </c>
       <c r="G36">
-        <v>-3.815865050508336</v>
+        <v>-4.413094086883937</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.37029566059797</v>
       </c>
       <c r="E37">
-        <v>-23.77293735039235</v>
+        <v>-24.246221754356</v>
       </c>
       <c r="F37">
-        <v>-4.208385541538404</v>
+        <v>-4.179359379520229</v>
       </c>
       <c r="G37">
-        <v>-3.478311895687628</v>
+        <v>-4.041061600271719</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.404517741263893</v>
       </c>
       <c r="E38">
-        <v>-23.09499309212604</v>
+        <v>-24.33527419571684</v>
       </c>
       <c r="F38">
-        <v>-4.293933375825654</v>
+        <v>-4.33021687020133</v>
       </c>
       <c r="G38">
-        <v>-2.894003918551802</v>
+        <v>-3.443968296263229</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.402747935487873</v>
       </c>
       <c r="E39">
-        <v>-22.97089931889385</v>
+        <v>-23.48321464032961</v>
       </c>
       <c r="F39">
-        <v>-4.422131994121604</v>
+        <v>-4.346946347639074</v>
       </c>
       <c r="G39">
-        <v>-3.774940086551865</v>
+        <v>-3.907924700864389</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.369224078193303</v>
       </c>
       <c r="E40">
-        <v>-21.67060687775341</v>
+        <v>-21.1586176064462</v>
       </c>
       <c r="F40">
-        <v>-4.423229502321004</v>
+        <v>-4.418700895255805</v>
       </c>
       <c r="G40">
-        <v>-3.367408620122043</v>
+        <v>-3.572844523561516</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.309924603490686</v>
       </c>
       <c r="E41">
-        <v>-21.42488734962321</v>
+        <v>-21.38577491961896</v>
       </c>
       <c r="F41">
-        <v>-4.539407000865811</v>
+        <v>-4.393120085456669</v>
       </c>
       <c r="G41">
-        <v>-3.202791743181783</v>
+        <v>-2.806340672671901</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.235578027822703</v>
       </c>
       <c r="E42">
-        <v>-20.88076402675757</v>
+        <v>-20.93171841629187</v>
       </c>
       <c r="F42">
-        <v>-4.579965709360216</v>
+        <v>-4.410599447645374</v>
       </c>
       <c r="G42">
-        <v>-2.999064081240574</v>
+        <v>-4.191989371407092</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.153356416102467</v>
       </c>
       <c r="E43">
-        <v>-20.43163903162484</v>
+        <v>-19.66359172602791</v>
       </c>
       <c r="F43">
-        <v>-4.515617362457037</v>
+        <v>-4.442868247525411</v>
       </c>
       <c r="G43">
-        <v>-3.361068925414338</v>
+        <v>-3.678517137175052</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.071677942558474</v>
       </c>
       <c r="E44">
-        <v>-19.77605637800841</v>
+        <v>-20.11742633412862</v>
       </c>
       <c r="F44">
-        <v>-4.620803941948695</v>
+        <v>-4.537089247258566</v>
       </c>
       <c r="G44">
-        <v>-2.752047725827854</v>
+        <v>-4.029481311975348</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.997730759375737</v>
       </c>
       <c r="E45">
-        <v>-20.01689421115834</v>
+        <v>-18.55308310207493</v>
       </c>
       <c r="F45">
-        <v>-4.549256859806887</v>
+        <v>-4.481276283386649</v>
       </c>
       <c r="G45">
-        <v>-3.393542066609049</v>
+        <v>-4.025998618068035</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.932987026507784</v>
       </c>
       <c r="E46">
-        <v>-19.10848232521966</v>
+        <v>-18.9241870185295</v>
       </c>
       <c r="F46">
-        <v>-4.432099047300422</v>
+        <v>-4.665154834257619</v>
       </c>
       <c r="G46">
-        <v>-3.691987746974347</v>
+        <v>-3.933276858604128</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.878780566883807</v>
       </c>
       <c r="E47">
-        <v>-17.89395465331049</v>
+        <v>-16.24042312567573</v>
       </c>
       <c r="F47">
-        <v>-4.266557435371368</v>
+        <v>-4.238340547075984</v>
       </c>
       <c r="G47">
-        <v>-3.869913016982477</v>
+        <v>-3.716793664700106</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.830384238114159</v>
       </c>
       <c r="E48">
-        <v>-16.61816578502555</v>
+        <v>-17.8136648091545</v>
       </c>
       <c r="F48">
-        <v>-4.497187776719068</v>
+        <v>-4.443769376191296</v>
       </c>
       <c r="G48">
-        <v>-2.950488446542848</v>
+        <v>-4.324983917356234</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.783494280216151</v>
       </c>
       <c r="E49">
-        <v>-16.82940551206135</v>
+        <v>-17.07143886234931</v>
       </c>
       <c r="F49">
-        <v>-4.254716066241627</v>
+        <v>-4.795869169400244</v>
       </c>
       <c r="G49">
-        <v>-3.504077871619775</v>
+        <v>-4.535365775831378</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.735262386101032</v>
       </c>
       <c r="E50">
-        <v>-17.18055697203813</v>
+        <v>-16.389948808935</v>
       </c>
       <c r="F50">
-        <v>-4.464048730438498</v>
+        <v>-4.308080620768274</v>
       </c>
       <c r="G50">
-        <v>-4.31673403787237</v>
+        <v>-4.086200888699682</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.681015461381003</v>
       </c>
       <c r="E51">
-        <v>-15.83815425110036</v>
+        <v>-16.42452823645757</v>
       </c>
       <c r="F51">
-        <v>-4.218112663271033</v>
+        <v>-4.238437153136825</v>
       </c>
       <c r="G51">
-        <v>-4.004175501873159</v>
+        <v>-4.221830628898083</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.621578582525622</v>
       </c>
       <c r="E52">
-        <v>-14.47941279594292</v>
+        <v>-16.53860049671078</v>
       </c>
       <c r="F52">
-        <v>-4.333061206025459</v>
+        <v>-4.68160399574833</v>
       </c>
       <c r="G52">
-        <v>-4.140718952640399</v>
+        <v>-4.331734119710807</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.556634362921832</v>
       </c>
       <c r="E53">
-        <v>-14.36041808444336</v>
+        <v>-14.52198950856303</v>
       </c>
       <c r="F53">
-        <v>-4.595171661707307</v>
+        <v>-4.241856374208259</v>
       </c>
       <c r="G53">
-        <v>-3.813054397345494</v>
+        <v>-4.76802098469474</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.488951411181291</v>
       </c>
       <c r="E54">
-        <v>-13.63870612489292</v>
+        <v>-14.78214581182969</v>
       </c>
       <c r="F54">
-        <v>-4.235966571908739</v>
+        <v>-4.908190344040956</v>
       </c>
       <c r="G54">
-        <v>-4.894609625025391</v>
+        <v>-5.579299964002997</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.423657653146764</v>
       </c>
       <c r="E55">
-        <v>-13.82961300363428</v>
+        <v>-13.67459428140371</v>
       </c>
       <c r="F55">
-        <v>-4.476110234690485</v>
+        <v>-4.484193469682888</v>
       </c>
       <c r="G55">
-        <v>-4.800921186264016</v>
+        <v>-4.585083548740153</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.363081659229929</v>
       </c>
       <c r="E56">
-        <v>-13.62707247516722</v>
+        <v>-11.93563762008826</v>
       </c>
       <c r="F56">
-        <v>-4.527813481711837</v>
+        <v>-4.460253379212148</v>
       </c>
       <c r="G56">
-        <v>-3.879953901603086</v>
+        <v>-5.427746499760702</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.314172421987189</v>
       </c>
       <c r="E57">
-        <v>-13.26289712394438</v>
+        <v>-12.11276435242427</v>
       </c>
       <c r="F57">
-        <v>-4.260461751302842</v>
+        <v>-4.276256842250477</v>
       </c>
       <c r="G57">
-        <v>-4.975386936183608</v>
+        <v>-4.420757999807349</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.281126095777544</v>
       </c>
       <c r="E58">
-        <v>-12.87546805869215</v>
+        <v>-12.34797782085668</v>
       </c>
       <c r="F58">
-        <v>-4.578151574234079</v>
+        <v>-4.957888619373361</v>
       </c>
       <c r="G58">
-        <v>-4.226395871196738</v>
+        <v>-5.460520900599486</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.268077234605555</v>
       </c>
       <c r="E59">
-        <v>-11.70042415165585</v>
+        <v>-11.79472509439158</v>
       </c>
       <c r="F59">
-        <v>-4.6414222092618</v>
+        <v>-4.573411542429169</v>
       </c>
       <c r="G59">
-        <v>-4.87304142083704</v>
+        <v>-5.100810264484436</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.279487475492062</v>
       </c>
       <c r="E60">
-        <v>-11.85303372571434</v>
+        <v>-11.83933509184114</v>
       </c>
       <c r="F60">
-        <v>-4.704310379310943</v>
+        <v>-4.856294676750879</v>
       </c>
       <c r="G60">
-        <v>-4.683194876341994</v>
+        <v>-4.749481929674821</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.314687200220433</v>
       </c>
       <c r="E61">
-        <v>-10.99059490790154</v>
+        <v>-12.20892649797715</v>
       </c>
       <c r="F61">
-        <v>-4.787778807731222</v>
+        <v>-4.996447899149524</v>
       </c>
       <c r="G61">
-        <v>-5.330664751821574</v>
+        <v>-5.615176346012079</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.375276776558757</v>
       </c>
       <c r="E62">
-        <v>-9.995014425789217</v>
+        <v>-11.47698471564339</v>
       </c>
       <c r="F62">
-        <v>-4.720464971501383</v>
+        <v>-5.005183620979087</v>
       </c>
       <c r="G62">
-        <v>-5.563743710513962</v>
+        <v>-5.756427392536163</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.457909879399141</v>
       </c>
       <c r="E63">
-        <v>-11.53806930153285</v>
+        <v>-10.36892599612855</v>
       </c>
       <c r="F63">
-        <v>-4.722945846817919</v>
+        <v>-5.040132843121005</v>
       </c>
       <c r="G63">
-        <v>-5.331416245658989</v>
+        <v>-6.318081306546755</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.557247388155746</v>
       </c>
       <c r="E64">
-        <v>-9.350549175861616</v>
+        <v>-10.18575375099229</v>
       </c>
       <c r="F64">
-        <v>-4.862009479546741</v>
+        <v>-4.790701536998165</v>
       </c>
       <c r="G64">
-        <v>-6.030424694093943</v>
+        <v>-6.24147528276802</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.667234310256241</v>
       </c>
       <c r="E65">
-        <v>-9.658163886728657</v>
+        <v>-9.883219987961859</v>
       </c>
       <c r="F65">
-        <v>-4.64045694050634</v>
+        <v>-5.148588191622129</v>
       </c>
       <c r="G65">
-        <v>-5.562820068308506</v>
+        <v>-6.29303371899663</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.776826028887366</v>
       </c>
       <c r="E66">
-        <v>-9.312414896243025</v>
+        <v>-9.557396283109975</v>
       </c>
       <c r="F66">
-        <v>-5.107162404139022</v>
+        <v>-4.93219536645423</v>
       </c>
       <c r="G66">
-        <v>-5.987490228995135</v>
+        <v>-6.671197335947578</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.876313706467568</v>
       </c>
       <c r="E67">
-        <v>-9.868357536268684</v>
+        <v>-9.161539727729471</v>
       </c>
       <c r="F67">
-        <v>-5.098501908340442</v>
+        <v>-5.562919708778271</v>
       </c>
       <c r="G67">
-        <v>-6.721656671057149</v>
+        <v>-7.206969404932148</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.953629342654648</v>
       </c>
       <c r="E68">
-        <v>-9.194937223536041</v>
+        <v>-9.025001707924202</v>
       </c>
       <c r="F68">
-        <v>-4.840139292707481</v>
+        <v>-5.439771528646657</v>
       </c>
       <c r="G68">
-        <v>-6.599140001739801</v>
+        <v>-6.980587679865706</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.9981880398589</v>
       </c>
       <c r="E69">
-        <v>-8.786840202912803</v>
+        <v>-9.49429199781309</v>
       </c>
       <c r="F69">
-        <v>-4.994951297059433</v>
+        <v>-5.582875195165766</v>
       </c>
       <c r="G69">
-        <v>-6.963051720144186</v>
+        <v>-7.71266516769244</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.003891485111837</v>
       </c>
       <c r="E70">
-        <v>-9.28136314997243</v>
+        <v>-8.430807047955751</v>
       </c>
       <c r="F70">
-        <v>-5.320992793135741</v>
+        <v>-5.015438908634516</v>
       </c>
       <c r="G70">
-        <v>-6.796799433707526</v>
+        <v>-6.999265777798273</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.966838221916158</v>
       </c>
       <c r="E71">
-        <v>-8.953809568049616</v>
+        <v>-9.894147195742367</v>
       </c>
       <c r="F71">
-        <v>-5.583894309922351</v>
+        <v>-5.315984323178164</v>
       </c>
       <c r="G71">
-        <v>-6.947068406280585</v>
+        <v>-5.941212112901663</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.887525147971556</v>
       </c>
       <c r="E72">
-        <v>-9.576080766865624</v>
+        <v>-9.516042258471931</v>
       </c>
       <c r="F72">
-        <v>-5.527085195029622</v>
+        <v>-5.48949831068554</v>
       </c>
       <c r="G72">
-        <v>-6.49166976189844</v>
+        <v>-6.873124061115424</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.768111558561926</v>
       </c>
       <c r="E73">
-        <v>-9.726145338531804</v>
+        <v>-10.08806098122482</v>
       </c>
       <c r="F73">
-        <v>-5.496469784125305</v>
+        <v>-5.162001388872944</v>
       </c>
       <c r="G73">
-        <v>-6.341281609685968</v>
+        <v>-7.112238144325903</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.611866724725327</v>
       </c>
       <c r="E74">
-        <v>-9.487417774269446</v>
+        <v>-10.14513333914349</v>
       </c>
       <c r="F74">
-        <v>-5.55736010916212</v>
+        <v>-5.593105935379504</v>
       </c>
       <c r="G74">
-        <v>-6.954934262481893</v>
+        <v>-6.816616359305604</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.422679981255303</v>
       </c>
       <c r="E75">
-        <v>-9.537869503188901</v>
+        <v>-10.45017134830016</v>
       </c>
       <c r="F75">
-        <v>-5.307048262550296</v>
+        <v>-5.713818375813172</v>
       </c>
       <c r="G75">
-        <v>-6.737279135456969</v>
+        <v>-6.744611993826456</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.204073946310415</v>
       </c>
       <c r="E76">
-        <v>-9.824965698327187</v>
+        <v>-10.8336470557437</v>
       </c>
       <c r="F76">
-        <v>-5.528769466270692</v>
+        <v>-6.06890820579047</v>
       </c>
       <c r="G76">
-        <v>-7.187102821150981</v>
+        <v>-7.303504912857296</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.9585677294316259</v>
       </c>
       <c r="E77">
-        <v>-9.795901952145957</v>
+        <v>-12.06479875573503</v>
       </c>
       <c r="F77">
-        <v>-5.765865287018174</v>
+        <v>-5.64181439451476</v>
       </c>
       <c r="G77">
-        <v>-6.402536633799103</v>
+        <v>-6.399398236627873</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.6876947247083711</v>
       </c>
       <c r="E78">
-        <v>-11.48244605529664</v>
+        <v>-10.95170890159767</v>
       </c>
       <c r="F78">
-        <v>-5.513239646063893</v>
+        <v>-5.966546957651957</v>
       </c>
       <c r="G78">
-        <v>-6.24493149231102</v>
+        <v>-6.217056698870356</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.3916423830905634</v>
       </c>
       <c r="E79">
-        <v>-11.69640286673704</v>
+        <v>-11.78307785924385</v>
       </c>
       <c r="F79">
-        <v>-6.096497946543341</v>
+        <v>-5.799332952276198</v>
       </c>
       <c r="G79">
-        <v>-6.038466009208832</v>
+        <v>-5.832692430124354</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.06719876817386417</v>
       </c>
       <c r="E80">
-        <v>-12.15059975275836</v>
+        <v>-13.84902204323116</v>
       </c>
       <c r="F80">
-        <v>-6.056168083553717</v>
+        <v>-5.925619245679255</v>
       </c>
       <c r="G80">
-        <v>-6.67895063360055</v>
+        <v>-5.634506621415884</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.2878160477695434</v>
       </c>
       <c r="E81">
-        <v>-12.21689208375665</v>
+        <v>-13.86116288204572</v>
       </c>
       <c r="F81">
-        <v>-5.963829318301062</v>
+        <v>-5.877663046853833</v>
       </c>
       <c r="G81">
-        <v>-5.927767987466683</v>
+        <v>-5.143873840859276</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.6764590408028542</v>
       </c>
       <c r="E82">
-        <v>-13.67572639990563</v>
+        <v>-14.52768632886468</v>
       </c>
       <c r="F82">
-        <v>-5.941620218395897</v>
+        <v>-5.891525224731675</v>
       </c>
       <c r="G82">
-        <v>-5.154547039677887</v>
+        <v>-5.340374581888256</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.098920774520982</v>
       </c>
       <c r="E83">
-        <v>-15.93202951727937</v>
+        <v>-14.43417334060629</v>
       </c>
       <c r="F83">
-        <v>-6.091201638035632</v>
+        <v>-6.347908489134001</v>
       </c>
       <c r="G83">
-        <v>-5.676785598497916</v>
+        <v>-6.046043847948225</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.551028174901179</v>
       </c>
       <c r="E84">
-        <v>-15.76661341872719</v>
+        <v>-16.25023632885035</v>
       </c>
       <c r="F84">
-        <v>-6.283696340939551</v>
+        <v>-6.394672949258054</v>
       </c>
       <c r="G84">
-        <v>-4.954212686914429</v>
+        <v>-4.700290533506791</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.027441212808727</v>
       </c>
       <c r="E85">
-        <v>-16.11152011304739</v>
+        <v>-15.82301103401871</v>
       </c>
       <c r="F85">
-        <v>-6.485829082118355</v>
+        <v>-6.555459484176002</v>
       </c>
       <c r="G85">
-        <v>-4.926559700024898</v>
+        <v>-4.304283076099171</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.514804438513902</v>
       </c>
       <c r="E86">
-        <v>-17.60622900028514</v>
+        <v>-17.89256894026414</v>
       </c>
       <c r="F86">
-        <v>-6.316003149761558</v>
+        <v>-6.669158482963146</v>
       </c>
       <c r="G86">
-        <v>-4.771718864062105</v>
+        <v>-5.063712291171363</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.996076662258725</v>
       </c>
       <c r="E87">
-        <v>-19.70982291717222</v>
+        <v>-19.99257177726314</v>
       </c>
       <c r="F87">
-        <v>-6.551835569114998</v>
+        <v>-6.305317490023609</v>
       </c>
       <c r="G87">
-        <v>-4.88180443487949</v>
+        <v>-4.884926279323023</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.449053828711843</v>
       </c>
       <c r="E88">
-        <v>-21.51289824196228</v>
+        <v>-21.76569124649246</v>
       </c>
       <c r="F88">
-        <v>-6.397424242359651</v>
+        <v>-6.439144599143031</v>
       </c>
       <c r="G88">
-        <v>-5.32700328845514</v>
+        <v>-4.94676064890553</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.849231496085988</v>
       </c>
       <c r="E89">
-        <v>-22.7565621156368</v>
+        <v>-23.11825586310344</v>
       </c>
       <c r="F89">
-        <v>-6.466799667764914</v>
+        <v>-6.19405106352258</v>
       </c>
       <c r="G89">
-        <v>-5.174913515835483</v>
+        <v>-5.306027671918318</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.174374432296675</v>
       </c>
       <c r="E90">
-        <v>-23.83073426415224</v>
+        <v>-24.2044828094273</v>
       </c>
       <c r="F90">
-        <v>-6.04284278198121</v>
+        <v>-6.270197227642824</v>
       </c>
       <c r="G90">
-        <v>-5.422161609435951</v>
+        <v>-3.905911889176512</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.402509373642527</v>
       </c>
       <c r="E91">
-        <v>-26.3703160730758</v>
+        <v>-27.21359944583616</v>
       </c>
       <c r="F91">
-        <v>-6.320012697212972</v>
+        <v>-6.328319234739451</v>
       </c>
       <c r="G91">
-        <v>-5.455210785554495</v>
+        <v>-5.080523241419782</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.516471325532228</v>
       </c>
       <c r="E92">
-        <v>-28.24288083151357</v>
+        <v>-29.40639071525232</v>
       </c>
       <c r="F92">
-        <v>-6.24613004477237</v>
+        <v>-6.550329464789415</v>
       </c>
       <c r="G92">
-        <v>-5.698317386685336</v>
+        <v>-5.115181342670413</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.503630785706861</v>
       </c>
       <c r="E93">
-        <v>-30.17336024403543</v>
+        <v>-30.94725154533925</v>
       </c>
       <c r="F93">
-        <v>-6.038120962794327</v>
+        <v>-6.320907491055195</v>
       </c>
       <c r="G93">
-        <v>-5.458316077270332</v>
+        <v>-6.067651778683048</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.355932691207997</v>
       </c>
       <c r="E94">
-        <v>-32.31433671385582</v>
+        <v>-32.4550114946671</v>
       </c>
       <c r="F94">
-        <v>-6.225309459028566</v>
+        <v>-5.914125499997954</v>
       </c>
       <c r="G94">
-        <v>-7.172195434587644</v>
+        <v>-4.944704800125643</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.074490061564719</v>
       </c>
       <c r="E95">
-        <v>-33.80060905401728</v>
+        <v>-35.36499983504805</v>
       </c>
       <c r="F95">
-        <v>-5.853813227620273</v>
+        <v>-5.990256618912</v>
       </c>
       <c r="G95">
-        <v>-6.884840081778904</v>
+        <v>-5.837880054984391</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.659644000127506</v>
       </c>
       <c r="E96">
-        <v>-36.88288092378305</v>
+        <v>-37.67621749247581</v>
       </c>
       <c r="F96">
-        <v>-5.099350774711117</v>
+        <v>-5.739509253173431</v>
       </c>
       <c r="G96">
-        <v>-6.689468236778815</v>
+        <v>-6.640674106075497</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.133195338335109</v>
       </c>
       <c r="E97">
-        <v>-38.79138591618269</v>
+        <v>-39.06106333605047</v>
       </c>
       <c r="F97">
-        <v>-5.767598653142622</v>
+        <v>-6.023711614522702</v>
       </c>
       <c r="G97">
-        <v>-7.495314610857129</v>
+        <v>-6.773910321849005</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.50052338654561</v>
       </c>
       <c r="E98">
-        <v>-42.01978258522796</v>
+        <v>-40.98941889426273</v>
       </c>
       <c r="F98">
-        <v>-5.195629800281385</v>
+        <v>-5.595392806721398</v>
       </c>
       <c r="G98">
-        <v>-7.118670534308706</v>
+        <v>-7.289795943779174</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.810184085165697</v>
       </c>
       <c r="E99">
-        <v>-44.66628166547262</v>
+        <v>-44.23556944565508</v>
       </c>
       <c r="F99">
-        <v>-4.86172203692309</v>
+        <v>-5.573403050085522</v>
       </c>
       <c r="G99">
-        <v>-8.008224052347492</v>
+        <v>-7.802880844183118</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.055955585042921</v>
       </c>
       <c r="E100">
-        <v>-46.6376848976018</v>
+        <v>-46.31366805387898</v>
       </c>
       <c r="F100">
-        <v>-4.713615443417108</v>
+        <v>-4.794799376054365</v>
       </c>
       <c r="G100">
-        <v>-8.457448529298896</v>
+        <v>-7.239012175206754</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.3306246496556068</v>
       </c>
       <c r="E101">
-        <v>-49.45044124044556</v>
+        <v>-50.18245094988944</v>
       </c>
       <c r="F101">
-        <v>-4.408341083009958</v>
+        <v>-5.174823863817299</v>
       </c>
       <c r="G101">
-        <v>-8.863635914239774</v>
+        <v>-7.569768780035337</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.4350856159956896</v>
       </c>
       <c r="E102">
-        <v>-51.43464533647592</v>
+        <v>-51.47026178454625</v>
       </c>
       <c r="F102">
-        <v>-3.926418581088776</v>
+        <v>-5.098471026075091</v>
       </c>
       <c r="G102">
-        <v>-9.595170472598069</v>
+        <v>-9.073504638156333</v>
       </c>
     </row>
   </sheetData>
